--- a/aq_files/0086.xlsx
+++ b/aq_files/0086.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher distributes questionnaires via email to collect responses from participants. Which method of data collection is used?</t>
-  </si>
-  <si>
-    <t>A surveyor visits households and asks questions face-to-face. Identify the data collection method.</t>
-  </si>
-  <si>
-    <t>A company collects customer feedback through an online Google Form. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher gathers data by directly observing customer behavior in a store without interacting with them. What method is used?</t>
-  </si>
-  <si>
-    <t>A census worker collects data from every household in a country. What type of data collection method is this?</t>
-  </si>
-  <si>
-    <t>A researcher records answers by calling participants over the phone. Identify the method used.</t>
-  </si>
-  <si>
-    <t>A scientist collects data from already published research papers and reports. What type of data collection is this?</t>
-  </si>
-  <si>
-    <t>A company installs cameras to observe how customers move inside a store. What method of data collection is applied?</t>
-  </si>
-  <si>
-    <t>A teacher collects data by asking students to fill out a printed questionnaire. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher conducts in-depth one-on-one discussions with participants. Identify the method.</t>
-  </si>
-  <si>
-    <t>A government collects population data from all citizens during a nationwide survey. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher collects data from books, journals, and websites instead of direct interaction. What type of data is this?</t>
-  </si>
-  <si>
-    <t>A company collects feedback using suggestion boxes placed in stores. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher gathers data by participating in group activities and observing behavior. Identify the method.</t>
-  </si>
-  <si>
-    <t>A survey collects data by sending SMS-based questionnaires. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher studies past records of a hospital to collect patient data. What type of data collection is used?</t>
-  </si>
-  <si>
-    <t>A company collects customer opinions through social media polls. What method is applied?</t>
-  </si>
-  <si>
-    <t>A researcher personally asks structured questions and records answers during interviews. What method is this?</t>
-  </si>
-  <si>
-    <t>A study collects data by measuring temperature and recording it directly using instruments. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher combines observation and interviews to gather detailed information. What type of data collection approach is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Order_Date,Sales_Amount,Quantity,Profit,Discount,Product_Category,Product_Name,Customer_Age,Customer_Segment,Order_Priority,Shipping_Days,Delivery_Status,Return_Flag,Satisfaction_Score,Units_Ordered,Unit_Price,Shipping_Cost,Payment_Terms</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,2024-01-05,1299.99,1,389.99,0.05,Electronics,MacBook Pro,45,Corporate,High,3,Delivered,FALSE,4.8,1,1299.99,15.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,2024-01-05,79.99,3,23.99,0.10,Electronics,Magic Mouse,45,Corporate,Medium,2,Delivered,FALSE,4.5,3,26.66,8.50,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,2024-01-06,89.99,2,26.99,0.00,Clothing,Designer Jeans,28,Consumer,Medium,4,Delivered,FALSE,4.2,2,44.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,2024-01-06,299.99,1,89.99,0.15,Electronics,27-inch Monitor,32,Consumer,High,3,Delivered,FALSE,4.9,1,299.99,18.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,2024-01-07,399.99,2,119.99,0.05,Furniture,Executive Chair,52,Corporate,High,5,Delivered,FALSE,5.0,2,199.99,22.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,2024-01-07,89.99,2,26.99,0.10,Electronics,Mechanical Keyboard,26,Consumer,Low,3,Delayed,FALSE,3.5,2,44.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,2024-01-08,199.99,1,59.99,0.20,Clothing,Leather Jacket,34,Home Office,Medium,4,Delivered,FALSE,4.7,1,199.99,15.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,2024-01-08,499.99,1,149.99,0.05,Electronics,iPad,41,Corporate,High,2,Delivered,FALSE,4.9,1,499.99,20.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,2024-01-09,79.99,2,23.99,0.00,Furniture,Floor Lamp,38,Consumer,Low,3,Delivered,FALSE,4.0,2,39.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,2024-01-09,69.99,1,20.99,0.10,Clothing,Running Shoes,29,Consumer,Medium,2,Returned,TRUE,2.8,1,69.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,2024-01-10,1299.99,1,389.99,0.15,Electronics,Gaming Laptop,35,Corporate,High,4,Delivered,FALSE,5.0,1,1299.99,25.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,2024-01-10,149.99,2,44.99,0.05,Electronics,Headphones,27,Consumer,Medium,3,Delivered,FALSE,4.3,2,74.99,12.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,2024-01-11,189.99,1,56.99,0.20,Clothing,Wool Coat,39,Home Office,Medium,4,Delivered,FALSE,4.5,1,189.99,15.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,2024-01-11,159.99,1,47.99,0.10,Furniture,Bookshelf,47,Corporate,Medium,5,Delivered,FALSE,4.2,1,159.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,2024-01-12,699.99,2,209.99,0.05,Electronics,Smartphone,31,Consumer,High,3,Delivered,FALSE,4.8,2,349.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,2024-01-12,59.99,3,17.99,0.00,Clothing,Dress Shirt,44,Corporate,Medium,2,Delivered,FALSE,4.4,3,20.00,10.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,2024-01-13,99.99,1,29.99,0.10,Electronics,External SSD,33,Consumer,Low,3,Delivered,FALSE,3.9,1,99.99,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,2024-01-13,49.99,2,14.99,0.05,Clothing,Hoodie,25,Consumer,Medium,2,Returned,TRUE,2.5,2,25.00,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,2024-01-14,349.99,1,104.99,0.15,Furniture,Gaming Desk,42,Corporate,High,4,Delivered,FALSE,4.9,1,349.99,25.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,2024-01-14,79.99,2,23.99,0.10,Electronics,Webcam,36,Home Office,Medium,3,Delivered,FALSE,4.6,2,39.99,8.50,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,129.99,1,38.99,0.00,Electronics,Docking Station,40,Consumer,Low,3,Delivered,FALSE,4.1,1,129.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,179.99,1,53.99,0.05,Clothing,Winter Parka,48,Consumer,Medium,4,Delivered,FALSE,4.3,1,179.99,15.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,449.99,1,134.99,0.10,Furniture,Office Desk,53,Corporate,High,5,Delivered,FALSE,4.9,1,449.99,22.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,39.99,3,11.99,0.00,Electronics,USB-C Hub,24,Consumer,Low,2,Delivered,FALSE,3.8,3,13.33,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,149.99,1,44.99,0.15,Clothing,Casual Blazer,37,Home Office,Medium,3,Delivered,FALSE,4.7,1,149.99,12.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,59.99,2,17.99,0.10,Electronics,Gaming Mouse,22,Consumer,Medium,2,Returned,TRUE,2.9,2,29.99,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,199.99,1,59.99,0.05,Electronics,Laser Printer,49,Corporate,High,4,Delivered,FALSE,4.8,1,199.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,279.99,1,83.99,0.20,Furniture,Lounge Chair,56,Consumer,Medium,5,Delivered,FALSE,4.2,1,279.99,22.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,49.99,4,14.99,0.00,Electronics,Power Bank,30,Consumer,Low,2,Delivered,FALSE,4.0,4,12.50,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,24.99,5,7.49,0.10,Clothing,Wool Scarf,26,Consumer,Medium,2,Delivered,FALSE,4.1,5,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,119.99,1,35.99,0.05,Electronics,Gaming Headset,34,Corporate,High,3,Delivered,FALSE,4.9,1,119.99,12.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,69.99,2,20.99,0.10,Furniture,Night Stand,44,Home Office,Medium,3,Delivered,FALSE,4.3,2,34.99,15.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,109.99,1,32.99,0.15,Clothing,Athletic Shoes,29,Consumer,Medium,2,Delivered,FALSE,4.5,1,109.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,199.99,1,59.99,0.05,Electronics,Smart Watch,38,Consumer,High,3,Delivered,FALSE,4.7,1,199.99,12.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,79.99,2,23.99,0.10,Electronics,Bluetooth Speaker,31,Corporate,Medium,3,Delivered,FALSE,4.4,2,39.99,10.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,99.99,1,29.99,0.00,Clothing,Cashmere Sweater,41,Consumer,Low,3,Returned,TRUE,2.7,1,99.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,129.99,1,38.99,0.05,Furniture,Bookshelf,46,Home Office,Medium,4,Delivered,FALSE,4.2,1,129.99,18.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,99.99,1,29.99,0.10,Electronics,Mesh Router,28,Consumer,Low,2,Delivered,FALSE,4.0,1,99.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,44.99,3,13.49,0.15,Clothing,Golf Polo,23,Consumer,Medium,2,Delivered,FALSE,4.3,3,15.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,499.99,1,149.99,0.20,Electronics,Graphics Card,43,Corporate,High,4,Delivered,FALSE,5.0,1,499.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,999.99,1,299.99,0.05,Electronics,Desktop PC,50,Corporate,High,3,Delivered,FALSE,4.9,1,999.99,25.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,49.99,2,14.99,0.00,Clothing,Yoga Pants,27,Consumer,Medium,2,Delivered,FALSE,4.4,2,25.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,249.99,1,74.99,0.10,Furniture,Coffee Table,55,Corporate,High,4,Delivered,FALSE,4.8,1,249.99,22.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,89.99,2,26.99,0.00,Electronics,Smart Speaker,34,Home Office,Medium,2,Delivered,FALSE,4.6,2,45.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,19.99,4,5.99,0.05,Clothing,Baseball Cap,19,Consumer,Low,2,Delivered,FALSE,3.5,4,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,349.99,1,104.99,0.10,Electronics,Quadcopter,38,Consumer,High,3,Delivered,FALSE,4.9,1,349.99,18.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,59.99,2,17.99,0.00,Furniture,Wall Mirror,42,Consumer,Medium,2,Delivered,FALSE,4.2,2,30.00,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,49.99,2,14.99,0.10,Clothing,Flannel Shirt,35,Home Office,Medium,3,Delivered,FALSE,4.1,2,25.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,29.99,3,8.99,0.05,Electronics,Streaming Stick,24,Consumer,Low,2,Returned,TRUE,2.6,3,10.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,29.99,4,8.99,0.00,Clothing,Leggings,22,Consumer,Medium,2,Delivered,FALSE,4.3,4,7.50,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Sales_Tier' that categorizes Sales_Amount: &gt;1000 = 'Premium', 500-1000 = 'High', 200-500 = 'Medium', &lt;200 = 'Low'</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Profit_Status' based on Profit: &gt;100 = 'Highly Profitable', &gt;0 = 'Profitable', =0 = 'Break Even', &lt;0 = 'Loss'</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Size' that categorizes Quantity: &gt;5 = 'Bulk Order', 3-5 = 'Standard Order', 1-2 = 'Small Order'</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Age_Group' based on Customer_Age: &lt;30 = 'Young', 30-50 = 'Middle', &gt;50 = 'Senior'</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Discount_Level' based on Discount: 0 = 'No Discount', 0.01-0.10 = 'Low Discount', 0.11-0.20 = 'High Discount'</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Shipping_Performance' based on Shipping_Days: &lt;=2 = 'Fast', 3-4 = 'Normal', &gt;=5 = 'Slow'</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Delivery_Status_Text' that converts Delivery_Status: 'Delivered' = 'On Time', 'Delayed' = 'Late', 'Returned' = 'Returned'</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Value' based on Sales_Amount and Quantity: If Sales_Amount &gt; 500 AND Quantity &gt; 1 then 'High Value', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Premium_Customer' based on Customer_Segment OR Order_Priority: If Corporate OR High then 'Premium', else 'Regular'</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Return_Risk' based on multiple conditions: If Discount &gt; 0.15 OR Satisfaction_Score &lt; 3 then 'High Risk', else 'Low Risk'</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Profitability' based on Profit and Quantity: If Profit &gt; 100 AND Quantity &gt; 1 then 'High', if Profit &gt; 50 then 'Medium', else 'Low'</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Shipping_Cost_Category' based on Shipping_Cost: &lt;10 = 'Low Cost', 10-20 = 'Medium Cost', &gt;20 = 'High Cost'</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Product_Priority' based on Category AND Order_Priority: If Electronics AND High then 'Urgent', else 'Normal'</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Payment_Risk' based on Payment_Terms: If COD then 'High Risk', if Net15 then 'Medium Risk', if Net30 then 'Low Risk'</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Sales_Efficiency' based on Units_Ordered and Unit_Price: If Units_Ordered &gt; 2 AND Unit_Price &gt; 100 then 'Efficient', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Return_Flag_Text' that converts Return_Flag: TRUE = 'Returned', FALSE = 'Not Returned'</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Value_Index' that uses a SWITCH function to assign values: 0-100 = 1, 101-500 = 2, 501-1000 = 3, &gt;1000 = 4</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Season' based on Order_Date month: 12,1,2 = 'Winter', 3,4,5 = 'Spring', 6,7,8 = 'Summer', 9,10,11 = 'Fall'</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Bulk_Discount_Flag' that checks if Quantity &gt; 5 AND Discount &gt; 0.05 THEN 'Eligible' ELSE 'Not Eligible'</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Tier' using nested IF with Customer_Segment, Satisfaction_Score, and Sales_Amount: If Corporate and Satisfaction &gt; 4.5 and Sales &gt; 500 then 'Platinum', if Corporate or Sales &gt; 500 then 'Gold', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>